--- a/data/trans_dic/IP11C$ingresado-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica</t>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,14</t>
+          <t>0,0; 27,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,58</t>
+          <t>0,0; 38,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,8</t>
+          <t>0,0; 48,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,72</t>
+          <t>0,0; 25,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 35,56</t>
+          <t>4,19; 36,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,75</t>
+          <t>0,0; 47,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,64</t>
+          <t>0,0; 20,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 29,06</t>
+          <t>2,99; 26,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,74; 35,3</t>
+          <t>3,63; 35,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,02</t>
+          <t>0,0; 46,8</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 20,19</t>
+          <t>2,22; 20,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,64</t>
+          <t>0,0; 61,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,18</t>
+          <t>0,0; 22,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,43</t>
+          <t>0,0; 17,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,43</t>
+          <t>0,0; 30,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,94</t>
+          <t>0,0; 11,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 12,8</t>
+          <t>1,66; 14,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,97</t>
+          <t>0,0; 18,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,38</t>
+          <t>0,0; 34,59</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,46</t>
+          <t>0,0; 38,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,02</t>
+          <t>0,0; 47,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,33</t>
+          <t>0,0; 51,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,13</t>
+          <t>0,0; 31,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,24</t>
+          <t>0,0; 23,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,64</t>
+          <t>0,0; 16,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 20,17</t>
+          <t>2,31; 19,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,04</t>
+          <t>0,0; 22,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,83</t>
+          <t>0,0; 26,21</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,36</t>
+          <t>0,0; 26,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,09</t>
+          <t>0,0; 24,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,75</t>
+          <t>0,0; 33,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,6</t>
+          <t>0,0; 16,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,77</t>
+          <t>0,0; 18,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,15</t>
+          <t>0,0; 25,88</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,51</t>
+          <t>0,0; 11,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,51</t>
+          <t>2,15; 12,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 20,42</t>
+          <t>2,0; 20,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 26,27</t>
+          <t>2,48; 29,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 13,22</t>
+          <t>1,78; 12,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 15,19</t>
+          <t>3,57; 14,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,42</t>
+          <t>0,0; 14,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,21</t>
+          <t>0,0; 14,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,48</t>
+          <t>1,33; 8,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,77; 11,87</t>
+          <t>3,88; 11,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 12,43</t>
+          <t>1,89; 12,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 15,48</t>
+          <t>2,72; 15,29</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1569</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3161</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2309</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3495</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3478</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3427</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3359</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>686; 6013</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4716</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1819</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5344</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>760; 6708</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>617; 5984</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2717</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1764</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2439</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476; 4462</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2769</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3021</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3479</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3355</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2438</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>679; 6064</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3646</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3609</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1151</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1927</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1151</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3306</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2122</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3360</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2767</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4225</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2540</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>616; 5122</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2782</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3888</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2842</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4839</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2556</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3225</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5850</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2618</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1741</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1159</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3294</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>8782</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4102</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1113; 6493</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>466; 4782</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>426; 5006</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>828; 5819</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2622; 10939</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 6094</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3587</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1090; 6957</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>4854; 14751</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1208; 7742</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1118; 6299</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$ingresado-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Habitat-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,12</t>
+          <t>0,0; 28,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,34</t>
+          <t>0,0; 31,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,99</t>
+          <t>0,0; 50,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,36</t>
+          <t>0,0; 29,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 36,73</t>
+          <t>4,24; 35,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,25</t>
+          <t>0,0; 40,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,82</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,45</t>
+          <t>0,0; 17,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 26,37</t>
+          <t>3,2; 27,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 35,25</t>
+          <t>3,76; 37,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,8</t>
+          <t>0,0; 51,64</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 20,82</t>
+          <t>0,0; 19,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,22 +872,22 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,09</t>
+          <t>0,0; 60,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,04</t>
+          <t>0,0; 21,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,84</t>
+          <t>0,0; 17,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,27</t>
+          <t>0,0; 23,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,75</t>
+          <t>0,0; 15,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 14,82</t>
+          <t>1,48; 13,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,19</t>
+          <t>0,0; 15,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,59</t>
+          <t>0,0; 27,54</t>
         </is>
       </c>
     </row>
@@ -1002,27 +1002,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,9</t>
+          <t>0,0; 37,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,53</t>
+          <t>0,0; 45,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,33</t>
+          <t>0,0; 52,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,1</t>
+          <t>0,0; 27,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,29</t>
+          <t>0,0; 24,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,68</t>
+          <t>0,0; 14,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 19,23</t>
+          <t>2,33; 19,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,51</t>
+          <t>0,0; 17,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,21</t>
+          <t>0,0; 28,28</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,59</t>
+          <t>0,0; 30,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,98</t>
+          <t>0,0; 24,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,91</t>
+          <t>0,0; 33,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,35</t>
+          <t>0,0; 13,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,24</t>
+          <t>0,0; 16,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,88</t>
+          <t>0,0; 25,52</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,62</t>
+          <t>0,0; 11,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 12,56</t>
+          <t>2,13; 12,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 20,46</t>
+          <t>2,03; 19,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 29,19</t>
+          <t>2,32; 26,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 12,51</t>
+          <t>1,4; 12,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 14,91</t>
+          <t>3,58; 15,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,96</t>
+          <t>0,0; 14,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,93</t>
+          <t>0,0; 15,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 8,5</t>
+          <t>1,47; 8,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 11,79</t>
+          <t>3,98; 11,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,08</t>
+          <t>1,79; 12,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,29</t>
+          <t>2,8; 16,65</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3495</t>
+          <t>0; 3631</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3478</t>
+          <t>0; 2859</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3427</t>
+          <t>0; 3535</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1665,42 +1665,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3359</t>
+          <t>0; 3950</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>686; 6013</t>
+          <t>693; 5819</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4716</t>
+          <t>0; 4013</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1819</t>
+          <t>0; 2308</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5344</t>
+          <t>0; 4660</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>760; 6708</t>
+          <t>813; 6999</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>617; 5984</t>
+          <t>639; 6432</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2717</t>
+          <t>0; 2998</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>476; 4462</t>
+          <t>0; 4237</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1868,22 +1868,22 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2769</t>
+          <t>0; 2756</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3021</t>
+          <t>0; 3000</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3479</t>
+          <t>0; 3430</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3355</t>
+          <t>0; 2645</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1893,22 +1893,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2438</t>
+          <t>0; 3252</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>679; 6064</t>
+          <t>606; 5346</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3646</t>
+          <t>0; 3138</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 3609</t>
+          <t>0; 2872</t>
         </is>
       </c>
     </row>
@@ -2066,27 +2066,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3306</t>
+          <t>0; 3213</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2122</t>
+          <t>0; 2048</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3360</t>
+          <t>0; 3415</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2767</t>
+          <t>0; 2416</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4225</t>
+          <t>0; 4520</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2540</t>
+          <t>0; 2163</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>616; 5122</t>
+          <t>619; 5083</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2782</t>
+          <t>0; 2126</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3888</t>
+          <t>0; 4196</t>
         </is>
       </c>
     </row>
@@ -2289,12 +2289,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2842</t>
+          <t>0; 3233</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4839</t>
+          <t>0; 4776</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2304,17 +2304,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2556</t>
+          <t>0; 2551</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3225</t>
+          <t>0; 2655</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5850</t>
+          <t>0; 5190</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 2618</t>
+          <t>0; 2581</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4102</t>
+          <t>0; 3891</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1113; 6493</t>
+          <t>1104; 6523</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>466; 4782</t>
+          <t>475; 4666</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>426; 5006</t>
+          <t>398; 4493</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>828; 5819</t>
+          <t>649; 6043</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2622; 10939</t>
+          <t>2626; 11425</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6094</t>
+          <t>0; 5980</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3587</t>
+          <t>0; 3831</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1090; 6957</t>
+          <t>1203; 7132</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4854; 14751</t>
+          <t>4976; 14887</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1208; 7742</t>
+          <t>1150; 8103</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1118; 6299</t>
+          <t>1151; 6858</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$ingresado-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15,02%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28,29%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,72%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,74%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>18,03%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27,28%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6,01%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,18</t>
+          <t>0,0; 29,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,51</t>
+          <t>4,12; 35,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,52</t>
+          <t>0,0; 47,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 78,86</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 33,14</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 31,58</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 57,8</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 29,83</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,24; 35,55</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 40,21</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,84</t>
+          <t>0,0; 18,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 27,51</t>
+          <t>3,15; 29,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 37,89</t>
+          <t>3,74; 35,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,64</t>
+          <t>0,0; 53,44</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,23%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13,01%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 22,18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 14,43</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 28,43</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 19,77</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 60,8</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 21,89</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,6</t>
+          <t>2,22; 20,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 59,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,67</t>
+          <t>0,0; 12,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 13,06</t>
+          <t>1,63; 12,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,66</t>
+          <t>0,0; 18,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,54</t>
+          <t>0,0; 27,44</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,38%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10,73%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 24,13</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 21,24</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 37,81</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 45,86</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,92</t>
+          <t>0,0; 31,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 48,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 52,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,21</t>
+          <t>0,0; 16,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 19,08</t>
+          <t>2,33; 20,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,21</t>
+          <t>0,0; 21,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,28</t>
+          <t>0,0; 25,8</t>
         </is>
       </c>
     </row>
@@ -1069,44 +1069,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,72%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3,26%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1137,52 +1137,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 26,36</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 25,09</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 37,57</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 30,25</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 24,65</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 33,84</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,46</t>
+          <t>0,0; 16,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,18</t>
+          <t>0,0; 18,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,52</t>
+          <t>0,0; 22,9</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>2,09%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,98%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>7,45%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,02</t>
+          <t>1,29; 13,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,61</t>
+          <t>2,85; 15,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 19,97</t>
+          <t>0,0; 13,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 26,2</t>
+          <t>0,0; 15,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,99</t>
+          <t>0,0; 12,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 15,57</t>
+          <t>1,29; 11,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,68</t>
+          <t>2,01; 20,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,94</t>
+          <t>2,09; 25,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,72</t>
+          <t>1,47; 8,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 11,9</t>
+          <t>3,77; 11,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 12,64</t>
+          <t>1,76; 12,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 16,65</t>
+          <t>2,2; 15,23</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1514,37 +1514,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,44 +1577,44 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>702</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1262</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2459</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>1569</t>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>626</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3631</t>
+          <t>0; 3936</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2859</t>
+          <t>675; 5822</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3535</t>
+          <t>0; 4766</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 1745</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4271</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2865</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4044</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3950</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>693; 5819</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4013</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2308</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4660</t>
+          <t>0; 4871</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>813; 6999</t>
+          <t>800; 7393</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>639; 6432</t>
+          <t>636; 5993</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2998</t>
+          <t>0; 3130</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,62 +1785,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1764</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2439</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>626</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>592</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0; 3039</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2813</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3151</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4237</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 2756</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3000</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3430</t>
+          <t>476; 4327</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2645</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2757</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3252</t>
+          <t>0; 2685</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>606; 5346</t>
+          <t>669; 5240</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3138</t>
+          <t>0; 3801</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2872</t>
+          <t>0; 2856</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,49 +1993,49 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>479</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1151</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>488</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>1927</t>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1034</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 2146</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3853</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3213</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2048</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3415</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2416</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4520</t>
+          <t>0; 2673</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2144</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3328</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2163</t>
+          <t>0; 2533</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>619; 5083</t>
+          <t>620; 5373</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2126</t>
+          <t>0; 2600</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4196</t>
+          <t>0; 3573</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,62 +2201,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>644</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>1255</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1255</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>453</t>
         </is>
       </c>
     </row>
@@ -2269,52 +2269,52 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0; 2817</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4860</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2534</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3233</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4776</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0; 2551</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2655</t>
+          <t>0; 3274</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5190</t>
+          <t>0; 6022</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 2581</t>
+          <t>0; 2134</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3093</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>1740</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2557</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1673</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2705</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3891</t>
+          <t>599; 6149</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1104; 6523</t>
+          <t>2089; 11146</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475; 4666</t>
+          <t>0; 5466</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>398; 4493</t>
+          <t>0; 3505</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>649; 6043</t>
+          <t>0; 4416</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2626; 11425</t>
+          <t>669; 5952</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5980</t>
+          <t>471; 4772</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3831</t>
+          <t>359; 4385</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1203; 7132</t>
+          <t>1204; 6940</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4976; 14887</t>
+          <t>4717; 14850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1150; 8103</t>
+          <t>1126; 7966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1151; 6858</t>
+          <t>869; 6005</t>
         </is>
       </c>
     </row>
